--- a/data/trans_orig/P41C_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P41C_R-Edad-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dificultades para tener un embarazo en 2023</t>
+          <t>Población con dificultades para tener un embarazo en 2023 (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4126</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2666</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3273</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56501</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60627</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64150</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121503</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124776</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16977</t>
+          <t>17579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13562</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25832</t>
+          <t>24437</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118452</t>
+          <t>117850</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>134189</t>
+          <t>134207</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>132866</t>
+          <t>132380</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>143342</t>
+          <t>143208</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>256026</t>
+          <t>257421</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>275673</t>
+          <t>275936</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19037</t>
+          <t>17160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18456</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>14210</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30727</t>
+          <t>31682</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>178565</t>
+          <t>180442</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>192687</t>
+          <t>192671</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>198329</t>
+          <t>198156</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>209445</t>
+          <t>209659</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>383660</t>
+          <t>382705</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>399808</t>
+          <t>400177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28645</t>
+          <t>29487</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16240</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38493</t>
+          <t>38961</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>426373</t>
+          <t>425531</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>453381</t>
+          <t>453647</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>229929</t>
+          <t>229837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>239981</t>
+          <t>239524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>662694</t>
+          <t>662226</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>694078</t>
+          <t>693851</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -2102,97 +2102,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1630</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1093</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1377</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29113</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30743</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20653</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52489</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>65-74</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2435,107 +2435,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26491</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44032</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29437</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21409</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40083</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55929</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35191</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75386</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -2548,107 +2548,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>564</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>852928</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>835387</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>869304</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>971</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>665842</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>655196</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>673870</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1518768</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1499311</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1539506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -2661,816 +2661,128 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>587</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>879419</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>879419</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>879419</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>695279</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>695279</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>695279</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1574697</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1574697</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1574697</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>26491</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>10962</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>44316</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>29437</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>21071</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>39850</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>55929</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>32890</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>75740</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>852928</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>835103</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>868457</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>94,96%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>971</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>665842</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>655429</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>674208</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>95,77%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>94,27%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1535</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1518768</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1498957</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1541807</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>95,19%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>879419</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>879419</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>879419</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>1013</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>695279</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>695279</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>695279</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>1574697</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>1574697</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>1574697</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A25:A27"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_orig/P41C_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P41C_R-Edad-trans_orig.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60627</t>
+          <t>56959</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64150</t>
+          <t>71326</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>124776</t>
+          <t>128285</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>60627</t>
+          <t>56959</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>60627</t>
+          <t>56959</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60627</t>
+          <t>56959</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64150</t>
+          <t>71326</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64150</t>
+          <t>71326</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>64150</t>
+          <t>71326</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>124776</t>
+          <t>128285</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>124776</t>
+          <t>128285</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>124776</t>
+          <t>128285</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17579</t>
+          <t>18640</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6768</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14048</t>
+          <t>13915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24437</t>
+          <t>28527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>129812</t>
+          <t>144849</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117850</t>
+          <t>132357</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>134207</t>
+          <t>149805</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>139660</t>
+          <t>155136</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>132380</t>
+          <t>148953</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>143208</t>
+          <t>159559</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>269473</t>
+          <t>299985</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>257421</t>
+          <t>285338</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>275936</t>
+          <t>306585</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>135429</t>
+          <t>150997</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>135429</t>
+          <t>150997</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>135429</t>
+          <t>150997</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>146428</t>
+          <t>162868</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>146428</t>
+          <t>162868</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>146428</t>
+          <t>162868</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>281858</t>
+          <t>313865</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>281858</t>
+          <t>313865</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>281858</t>
+          <t>313865</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>11114</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17160</t>
+          <t>19271</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18629</t>
+          <t>19923</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>24065</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14210</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31682</t>
+          <t>35139</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>187760</t>
+          <t>209484</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>180442</t>
+          <t>201327</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>192671</t>
+          <t>214954</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>204878</t>
+          <t>234414</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>198156</t>
+          <t>227442</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>209659</t>
+          <t>239668</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>392638</t>
+          <t>443898</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>382705</t>
+          <t>432824</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>400177</t>
+          <t>451178</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>197602</t>
+          <t>220598</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>197602</t>
+          <t>220598</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>197602</t>
+          <t>220598</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>216785</t>
+          <t>247365</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>216785</t>
+          <t>247365</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>216785</t>
+          <t>247365</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>414387</t>
+          <t>467963</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>414387</t>
+          <t>467963</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>414387</t>
+          <t>467963</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11033</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>5747</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29487</t>
+          <t>20067</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10762</t>
+          <t>11086</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>21794</t>
+          <t>22380</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38961</t>
+          <t>32965</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>443985</t>
+          <t>219815</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>425531</t>
+          <t>211041</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>453647</t>
+          <t>225361</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>235407</t>
+          <t>257371</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>229837</t>
+          <t>251616</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>239524</t>
+          <t>261484</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>679393</t>
+          <t>477185</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>662226</t>
+          <t>466600</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>693851</t>
+          <t>484336</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>455018</t>
+          <t>231108</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>455018</t>
+          <t>231108</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>455018</t>
+          <t>231108</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>246169</t>
+          <t>268457</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>246169</t>
+          <t>268457</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>246169</t>
+          <t>268457</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>701187</t>
+          <t>499565</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>701187</t>
+          <t>499565</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>701187</t>
+          <t>499565</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30743</t>
+          <t>36093</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>52489</t>
+          <t>59673</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30743</t>
+          <t>36093</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30743</t>
+          <t>36093</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30743</t>
+          <t>36093</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>52489</t>
+          <t>59673</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52489</t>
+          <t>59673</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52489</t>
+          <t>59673</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>26491</t>
+          <t>28556</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44032</t>
+          <t>45806</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29437</t>
+          <t>31769</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21409</t>
+          <t>23090</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40083</t>
+          <t>42269</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>55929</t>
+          <t>60325</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35191</t>
+          <t>46801</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75386</t>
+          <t>79563</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>852928</t>
+          <t>667199</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>835387</t>
+          <t>649949</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>869304</t>
+          <t>677410</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>665842</t>
+          <t>741827</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>655196</t>
+          <t>731327</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>673870</t>
+          <t>750506</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1518768</t>
+          <t>1409027</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1499311</t>
+          <t>1389789</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1539506</t>
+          <t>1422551</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>879419</t>
+          <t>695755</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1574697</t>
+          <t>1469352</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
